--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0155.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0155.xlsx
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Đừng có mà ngủ lúc này, ông bạn già. Ngươi là người trò chuyện duy nhất ta có đấy.</t>
+          <t>Đừng có mà ngủ lúc này, ông bạn già. Mày là người trò chuyện duy nhất tao có đấy.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Chân, Mô-đun Năng Lượng, Động Cơ... Xem ra là đủ hết rồi. Giờ thì sửa con robot thôi.</t>
+          <t>Chân, Module Năng Lượng, Động Cơ... Xem ra là đủ hết rồi. Giờ thì sửa con robot thôi.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Ta sẽ mang tiền đến ngay bây giờ. Cậu giữ cái máy đó ấm áp cho ta nhé, được chứ? Ta đang trông cậy vào nó đấy!</t>
+          <t>Tao sẽ mang tiền đến ngay bây giờ. Cậu giữ cái máy đó ấm áp cho tao nhé, được chứ? Tao đang trông cậy vào nó đấy!</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Hừ, vụ này hốt bạc to đấy... Ê, ngươi đang ngó nghiêng cái gì thế? Có việc gì thì đi mà nói chuyện với ông chủ ta!</t>
+          <t>Hừ, vụ này hốt bạc to đấy... Ê, mày đang ngó nghiêng cái gì thế? Có việc gì thì đi mà nói chuyện với ông chủ tao!</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sao cơ?</t>
+          <t>Lại đến nữa à?</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Ta nghĩ kỹ năng bắn súng của ta cũng tạm ổn.</t>
+          <t>Tao nghĩ kỹ năng bắn súng của tao cũng tạm ổn.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tuyệt! Ta biết ngươi làm được mà. Lối này, phần thưởng đang chờ đấy!</t>
+          <t>Tuyệt! Tao biết mày làm được mà. Lối này, phần thưởng đang chờ đấy!</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Ngươi đúng là gặp may rồi, bọn ta đang có ưu đãi giảm 20% nếu gia nhập ngay bây giờ! Tổng cộng chỉ còn... 500 Credits phí đăng ký thôi!</t>
+          <t>Mày đúng là gặp may rồi, bọn tao đang có ưu đãi giảm 20% nếu gia nhập ngay bây giờ! Tổng cộng chỉ còn... 500 Credits phí đăng ký thôi!</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Ý anh là sao? Ta là người giữ lời đấy, 1000 Credits, đưa đây!</t>
+          <t>Ý anh là sao? Tao là người giữ lời đấy, 1000 Credits, đưa đây!</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi, SHC nhiều quá, lần này ta kiếm bộn rồi.</t>
+          <t>Được rồi, được rồi, SHC nhiều quá, lần này tao kiếm bộn rồi.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Sao, ngươi có vấn đề gì à?</t>
+          <t>Sao, mày có vấn đề gì à?</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hừ, có gì đâu? Ta đâu có định để tụi bay thắng ngay từ đầu.</t>
+          <t>Hừ, có gì đâu? Tao đâu có định để tụi bay thắng ngay từ đầu.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Cậu sẽ không thoát được đâu.</t>
+          <t>Mày sẽ không thoát được đâu.</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Cậu sắp toi rồi!</t>
+          <t>Mày sắp toi rồi!</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Hừ. Ngươi có biết ta là ai không? Đánh chúng nó đi, anh em!</t>
+          <t>Hừ. Mày có biết tao là ai không? Đánh chúng nó đi, anh em!</t>
         </is>
       </c>
     </row>
